--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -577,14 +577,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45597</v>
+        <v>45323</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -635,18 +635,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45627</v>
+        <v>45352</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -693,18 +693,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ene 25</t>
+          <t>Jun 24</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45658</v>
+        <v>45444</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -751,11 +751,11 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>0.2</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -809,18 +809,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Dic 24</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45717</v>
+        <v>45627</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -867,18 +867,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Abr 25</t>
+          <t>Ene 25</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45748</v>
+        <v>45658</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -925,18 +925,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>May 25</t>
+          <t>Feb 25</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45778</v>
+        <v>45689</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -983,18 +983,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Jun 25</t>
+          <t>Mar 25</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45809</v>
+        <v>45717</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Abr 25</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>45839</v>
+        <v>45748</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1099,11 +1099,11 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Ago 25</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>45870</v>
+        <v>45778</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>0.1</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1157,18 +1157,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45901</v>
+        <v>45809</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>45931</v>
+        <v>45839</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1273,18 +1273,18 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45962</v>
+        <v>45870</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1331,18 +1331,18 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>45992</v>
+        <v>45901</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1389,18 +1389,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Ene 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1447,18 +1447,18 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>46054</v>
+        <v>45962</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -1505,18 +1505,18 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>46082</v>
+        <v>45992</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1563,11 +1563,11 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>0.3</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1621,18 +1621,18 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>46143</v>
+        <v>46054</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1679,56 +1679,230 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>21 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>+0.3%</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+0.3%</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>21 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>+1.1%</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>21 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B28" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C28" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>+0.2%</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>+1.7%</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Variación mensual estimada (%)</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Serie desestacionalizada</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>21 de julio de 2026</t>
         </is>

--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -577,14 +577,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Feb 24</t>
+          <t>Dic 23</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45323</v>
+        <v>45261</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -635,18 +635,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Mar 24</t>
+          <t>Ene 24</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -693,18 +693,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Jun 24</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45444</v>
+        <v>45323</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -751,11 +751,11 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45597</v>
+        <v>45352</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>0.2</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -809,18 +809,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Abr 24</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45627</v>
+        <v>45383</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -867,18 +867,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Ene 25</t>
+          <t>May 24</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45658</v>
+        <v>45413</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -925,18 +925,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Jun 24</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45689</v>
+        <v>45444</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -983,18 +983,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45717</v>
+        <v>45597</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Abr 25</t>
+          <t>Dic 24</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>45748</v>
+        <v>45627</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1099,11 +1099,11 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>May 25</t>
+          <t>Ene 25</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>45778</v>
+        <v>45658</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>0.1</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1157,11 +1157,11 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Jun 25</t>
+          <t>Feb 25</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45809</v>
+        <v>45689</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>0.2</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Mar 25</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>45839</v>
+        <v>45717</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1273,18 +1273,18 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ago 25</t>
+          <t>Abr 25</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45870</v>
+        <v>45748</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1331,11 +1331,11 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>45901</v>
+        <v>45778</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0.1</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1389,18 +1389,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45931</v>
+        <v>45809</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1447,18 +1447,18 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>45962</v>
+        <v>45839</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -1505,28 +1505,28 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45992</v>
+        <v>45870</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
           <t>+0.2%</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+2.3%</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1563,18 +1563,18 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Ene 26</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>46023</v>
+        <v>45901</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1621,18 +1621,18 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>46054</v>
+        <v>45931</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1679,28 +1679,28 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>46082</v>
+        <v>45962</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>+0.5%</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1737,18 +1737,18 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>46113</v>
+        <v>45992</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1795,18 +1795,18 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>46143</v>
+        <v>46023</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -1853,56 +1853,288 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>21 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>21 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>+0.3%</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>+0.3%</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>21 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>+1.1%</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>21 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B32" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C32" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>+0.2%</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>+1.7%</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Variación mensual estimada (%)</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Serie desestacionalizada</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>21 de julio de 2026</t>
         </is>

--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -18,7 +18,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>

--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf · Fecha de publicación: 21 de julio de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf · Fecha de publicación: 20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,70 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>20 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>+2.7%</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -983,18 +983,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Jul 24</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45597</v>
+        <v>45474</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>45627</v>
+        <v>45597</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1099,18 +1099,18 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Ene 25</t>
+          <t>Dic 24</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>45658</v>
+        <v>45627</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1157,18 +1157,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Ene 25</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Feb 25</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1273,11 +1273,11 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Abr 25</t>
+          <t>Mar 25</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1331,18 +1331,18 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>May 25</t>
+          <t>Abr 25</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1389,18 +1389,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Jun 25</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1447,18 +1447,18 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -1505,28 +1505,28 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Ago 25</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
           <t>+0.1%</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+0.2%</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1563,11 +1563,11 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>0.1</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1621,18 +1621,18 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1679,18 +1679,18 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1737,18 +1737,18 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1795,18 +1795,18 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Ene 26</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1853,18 +1853,18 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1911,18 +1911,18 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -1969,18 +1969,18 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2027,18 +2027,18 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Abr 26</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -2085,18 +2085,18 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2143,56 +2143,114 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>+0.2%</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>+1.7%</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>20 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B34" s="5" t="n">
         <v>46204</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C34" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>+0.1%</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>+2.7%</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Variación mensual estimada (%)</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Serie desestacionalizada</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>20 de agosto de 2026</t>
         </is>
